--- a/hardware/luxdmx_BOM_jlcpcb.xlsx
+++ b/hardware/luxdmx_BOM_jlcpcb.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,254 +837,254 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>600R@100MHz ferrite bead 0805 (+5V to DMX DC-DC)</t>
+          <t>TBU-CA065-200-WH 200mA 650V high-speed protector (DMX Protected series)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FB1,FB2,FB3</t>
+          <t>F2,F3,F4,F5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>L_0805_2012Metric</t>
+          <t>DIO-SMD_3P-L6.5-W4.0-BI</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C139168</t>
+          <t>C913221</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Neutrik NC5FAH XLR-5 female horizontal PCB (E1.11 DMX out)</t>
+          <t>600R@100MHz ferrite bead 0805 (+5V to DMX DC-DC)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>J1,J5</t>
+          <t>FB1,FB2,FB3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CONN-TH_NC5FAH</t>
+          <t>L_0805_2012Metric</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C368501</t>
+          <t>C139168</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>USB-C data (TYPE-C-31-M-12)</t>
+          <t>Neutrik NC5FAH XLR-5 female horizontal PCB (E1.11 DMX out)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1,J5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USB-C_SMD-TYPE-C-31-M-12_1</t>
+          <t>CONN-TH_NC5FAH</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C165948</t>
+          <t>C368501</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RJ45 MagJack HY931147C PoE 10/100 (integrated rectifier + magnetics)</t>
+          <t>USB-C data (TYPE-C-31-M-12)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RJ45-TH_HY931147C</t>
+          <t>USB-C_SMD-TYPE-C-31-M-12_1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C91754</t>
+          <t>C165948</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JST SH 1.0mm 9-pin SMD SM09B-SRSS-TB (optional display; pre-crimped cables)</t>
+          <t>RJ45 MagJack HY931147C PoE 10/100 (integrated rectifier + magnetics)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>J4,J6</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JST_SH_SM09B-SRSS-TB_1x09-1MP_P1.00mm_Horizontal</t>
+          <t>RJ45-TH_HY931147C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>C160408</t>
+          <t>C91754</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JST SH 1.0mm 3-pin SMD SM03B-SRSS-TB (DMX-A breakout)</t>
+          <t>JST SH 1.0mm 9-pin SMD SM09B-SRSS-TB (optional display; pre-crimped cables)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>J7,J8</t>
+          <t>J4,J6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JST_SH_SM03B-SRSS-TB_1x03-1MP_P1.00mm_Horizontal</t>
+          <t>JST_SH_SM09B-SRSS-TB_1x09-1MP_P1.00mm_Horizontal</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C160403</t>
+          <t>C160408</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2.2uH power inductor (CKCS4030)</t>
+          <t>JST SH 1.0mm 3-pin SMD SM03B-SRSS-TB (DMX-A breakout)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>J7,J8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IND-SMD_L4.0-W4.0</t>
+          <t>JST_SH_SM03B-SRSS-TB_1x03-1MP_P1.00mm_Horizontal</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>C354584</t>
+          <t>C160403</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ACM2012-201-2P common-mode choke (DMX-A pair)</t>
+          <t>2.2uH power inductor (CKCS4030)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L2,L3</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>L_CommonModeChoke_Coilank_ACM2012</t>
+          <t>IND-SMD_L4.0-W4.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C383338</t>
+          <t>C354584</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0505S-1W iso DC-DC (EVISUN)</t>
+          <t>ACM2012-201-2P common-mode choke (DMX-A pair)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PS1,PS2</t>
+          <t>L2,L3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PWRM-TH_B0505S-1W</t>
+          <t>L_CommonModeChoke_Coilank_ACM2012</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>C7465127</t>
+          <t>C383338</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MMBT3904 SOT-23</t>
+          <t>B0505S-1W iso DC-DC (EVISUN)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q1,Q2</t>
+          <t>PS1,PS2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>PWRM-TH_B0505S-1W</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>C20526</t>
+          <t>C7465127</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10k 0402</t>
+          <t>MMBT3904 SOT-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R1,R2,R6,R7,R11</t>
+          <t>Q1,Q2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C25744</t>
+          <t>C20526</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>12k 0402 W5500 EXRES1 (12.4k spec OOS at LCSC; 12k within 100BASE-TX +-5%)</t>
+          <t>10k 0402</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R1,R2,R6,R7,R11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,19 +1094,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C25752</t>
+          <t>C25744</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>330R 0402</t>
+          <t>12k 0402 W5500 EXRES1 (12.4k spec OOS at LCSC; 12k within 100BASE-TX +-5%)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R4,R5</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1116,19 +1116,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C25104</t>
+          <t>C25752</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5k1 0402</t>
+          <t>330R 0402</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R8,R9</t>
+          <t>R4,R5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1138,19 +1138,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C25905</t>
+          <t>C25104</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>45.3k 0402 1% (buck FB top -&gt; 3.32V)</t>
+          <t>5k1 0402</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R8,R9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1160,63 +1160,63 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C137977</t>
+          <t>C25905</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>120R 0805 (DMX-A termination)</t>
+          <t>45.3k 0402 1% (buck FB top -&gt; 3.32V)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R12,R19</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C17437</t>
+          <t>C137977</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1k 0402</t>
+          <t>120R 0805 (DMX-A termination)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R13,R15</t>
+          <t>R12,R19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C11702</t>
+          <t>C17437</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>150R 0402</t>
+          <t>1k 0402</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R14,R16,R17</t>
+          <t>R13,R15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1226,19 +1226,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C25082</t>
+          <t>C11702</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>49.9R 1% 0402 W5500 TX center-tap bias</t>
+          <t>150R 0402</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R14,R16,R17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1248,225 +1248,269 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C25120</t>
+          <t>C25082</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tact sw B3U-1000P</t>
+          <t>49.9R 1% 0402 W5500 TX center-tap bias</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SW1,SW2</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SW_SPST_B3U-1000P</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C231329</t>
+          <t>C25120</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ESP32-S3-WROOM-1-N8 (8MB)</t>
+          <t>470R 0402 (DMX-A fail-safe bias)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>R20,R21,R22,R23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ESP32-S3-WROOM-1</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C2913198</t>
+          <t>C25117</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>W5500 SPI Ethernet</t>
+          <t>tact sw B3U-1000P</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>SW1,SW2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LQFP-48_L7.0-W7.0-P0.50-LS9.0-BL</t>
+          <t>SW_SPST_B3U-1000P</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C32843</t>
+          <t>C231329</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CH340C USB-UART</t>
+          <t>ESP32-S3-WROOM-1-N8 (8MB)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SOP-16_L10.0-W3.9-P1.27-LS6.0-BL</t>
+          <t>ESP32-S3-WROOM-1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C84681</t>
+          <t>C2913198</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SY8089 buck 5-&gt;3.3V</t>
+          <t>W5500 SPI Ethernet</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
+          <t>LQFP-48_L7.0-W7.0-P0.50-LS9.0-BL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C78988</t>
+          <t>C32843</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ISO3086DWR isolated RS-485</t>
+          <t>CH340C USB-UART</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U5,U6</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SOIC-16_L10.3-W7.5-P1.27-LS10.3-BL</t>
+          <t>SOP-16_L10.0-W3.9-P1.27-LS6.0-BL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C183095</t>
+          <t>C84681</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DP9900M-5V PoE PD + isolated DC-DC module (802.3af)</t>
+          <t>SY8089 buck 5-&gt;3.3V</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PWRM-SMD_DP9900M-5V</t>
+          <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C5380106</t>
+          <t>C78988</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>USBLC6-2SC6 USB ESD/TVS array (SOT-23-6)</t>
+          <t>ISO3086DWR isolated RS-485</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U5,U6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>SOIC-16_L10.3-W7.5-P1.27-LS10.3-BL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>C7519</t>
+          <t>C183095</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TPS2116DRLR ideal-diode power mux (USB/PoE 5V OR-ing)</t>
+          <t>DP9900M-5V PoE PD + isolated DC-DC module (802.3af)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SOT-583-8</t>
+          <t>PWRM-SMD_DP9900M-5V</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C3235557</t>
+          <t>C5380106</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>USBLC6-2SC6 USB ESD/TVS array (SOT-23-6)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>U8</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SOT-23-6</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>C7519</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TPS2116DRLR ideal-diode power mux (USB/PoE 5V OR-ing)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>U9</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SOT-583-8</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>C3235557</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>25MHz crystal 2520</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Crystal_SMD_2520-4Pin_2.5x2.0mm</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>C2981622</t>
         </is>

--- a/hardware/luxdmx_BOM_jlcpcb.xlsx
+++ b/hardware/luxdmx_BOM_jlcpcb.xlsx
@@ -529,7 +529,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22pF 0402</t>
+          <t>10pF 0402 C0G (W5500 xtal load)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C1555</t>
+          <t>C32949</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C139168</t>
+          <t>C1017</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C25744</t>
+          <t>C60490</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C25104</t>
+          <t>C2930002</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C137977</t>
+          <t>C2933099</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C11702</t>
+          <t>C106235</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C25082</t>
+          <t>C2909321</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C25117</t>
+          <t>C2909361</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C84681</t>
+          <t>C7464026</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25MHz crystal 2520</t>
+          <t>25MHz crystal 2520 (CL=9pF; in-stock C2981624)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>C2981622</t>
+          <t>C2981624</t>
         </is>
       </c>
     </row>

--- a/hardware/luxdmx_BOM_jlcpcb.xlsx
+++ b/hardware/luxdmx_BOM_jlcpcb.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C1,C5,C8,C9,C10,C11,C14,C15,C18,C19,C22,C23,C24</t>
+          <t>C1,C5,C8,C9,C10,C11,C14,C18,C19,C22,C23,C24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10pF 0402 C0G (W5500 xtal load)</t>
+          <t>18pF 0402 C0G (W5500 xtal load, CL=12pF)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C32949</t>
+          <t>C307443</t>
         </is>
       </c>
     </row>
@@ -1057,34 +1057,34 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MMBT3904 SOT-23</t>
+          <t>10k 0402</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Q1,Q2</t>
+          <t>R1,R2,R11,R25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C20526</t>
+          <t>C60490</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10k 0402</t>
+          <t>12k 0402 W5500 EXRES1 (12.4k spec OOS at LCSC; 12k within 100BASE-TX +-5%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R1,R2,R6,R7,R11</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,19 +1094,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C60490</t>
+          <t>C25752</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>12k 0402 W5500 EXRES1 (12.4k spec OOS at LCSC; 12k within 100BASE-TX +-5%)</t>
+          <t>330R 0402</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4,R5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1116,19 +1116,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C25752</t>
+          <t>C2930002</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>330R 0402</t>
+          <t>5k1 0402</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R4,R5</t>
+          <t>R8,R9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1138,19 +1138,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C2930002</t>
+          <t>C25905</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5k1 0402</t>
+          <t>45.3k 0402 1% (buck FB top -&gt; 3.32V)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R8,R9</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1160,63 +1160,63 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C25905</t>
+          <t>C2933099</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>45.3k 0402 1% (buck FB top -&gt; 3.32V)</t>
+          <t>120R 0805 (DMX-A termination)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R12,R19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C2933099</t>
+          <t>C17437</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>120R 0805 (DMX-A termination)</t>
+          <t>1k 0402</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R12,R19</t>
+          <t>R13,R15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C17437</t>
+          <t>C106235</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1k 0402</t>
+          <t>150R 0402</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R13,R15</t>
+          <t>R14,R16,R17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1226,19 +1226,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C106235</t>
+          <t>C2909321</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>150R 0402</t>
+          <t>49.9R 1% 0402 W5500 TX center-tap bias</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R14,R16,R17</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1248,19 +1248,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C2909321</t>
+          <t>C25120</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>49.9R 1% 0402 W5500 TX center-tap bias</t>
+          <t>470R 0402 (DMX-A fail-safe bias)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R20,R21,R22,R23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C25120</t>
+          <t>C2909361</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>470R 0402 (DMX-A fail-safe bias)</t>
+          <t>30k 0402 1% (TPS2116 PR1 divider top, Vsw=4.0V)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R20,R21,R22,R23</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C2909361</t>
+          <t>C138008</t>
         </is>
       </c>
     </row>
@@ -1365,154 +1365,132 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CH340C USB-UART</t>
+          <t>SY8089 buck 5-&gt;3.3V</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SOP-16_L10.0-W3.9-P1.27-LS6.0-BL</t>
+          <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C7464026</t>
+          <t>C78988</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SY8089 buck 5-&gt;3.3V</t>
+          <t>ISO3086DWR isolated RS-485</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U5,U6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
+          <t>SOIC-16_L10.3-W7.5-P1.27-LS10.3-BL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C78988</t>
+          <t>C183095</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ISO3086DWR isolated RS-485</t>
+          <t>DP9900M-5V PoE PD + isolated DC-DC module (802.3af)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U5,U6</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SOIC-16_L10.3-W7.5-P1.27-LS10.3-BL</t>
+          <t>PWRM-SMD_DP9900M-5V</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>C183095</t>
+          <t>C5380106</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DP9900M-5V PoE PD + isolated DC-DC module (802.3af)</t>
+          <t>USBLC6-2SC6 USB ESD/TVS array (SOT-23-6)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PWRM-SMD_DP9900M-5V</t>
+          <t>SOT-23-6</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C5380106</t>
+          <t>C7519</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>USBLC6-2SC6 USB ESD/TVS array (SOT-23-6)</t>
+          <t>TPS2116DRLR ideal-diode power mux (USB/PoE 5V OR-ing)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>SOT-583-8</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>C7519</t>
+          <t>C3235557</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TPS2116DRLR ideal-diode power mux (USB/PoE 5V OR-ing)</t>
+          <t>25MHz crystal 3225 SMD (C9006 X322525MOB4SI, CL=12pF, mainstream/always-in-stock pkg)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SOT-583-8</t>
+          <t>Crystal_SMD_3225-4Pin_3.2x2.5mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>C3235557</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>25MHz crystal 2520 (CL=9pF; in-stock C2981624)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Crystal_SMD_2520-4Pin_2.5x2.0mm</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>C2981624</t>
+          <t>C9006</t>
         </is>
       </c>
     </row>

--- a/hardware/luxdmx_BOM_jlcpcb.xlsx
+++ b/hardware/luxdmx_BOM_jlcpcb.xlsx
@@ -1321,7 +1321,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ESP32-S3-WROOM-1-N8 (8MB)</t>
+          <t>ESP32-S3-WROOM-1-N8R2 (8MB flash + 2MB quad PSRAM; quad keeps IO35/36/37 free, octal R8 would not)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C2913198</t>
+          <t>C2913204</t>
         </is>
       </c>
     </row>

--- a/hardware/luxdmx_BOM_jlcpcb.xlsx
+++ b/hardware/luxdmx_BOM_jlcpcb.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C1,C5,C8,C9,C10,C11,C14,C15,C18,C19,C22,C23,C24</t>
+          <t>C1,C5,C8,C9,C10,C11,C14,C18,C19,C22,C23,C24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10pF 0402 C0G (W5500 xtal load)</t>
+          <t>18pF 0402 C0G (W5500 xtal load, CL=12pF)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C32949</t>
+          <t>C307443</t>
         </is>
       </c>
     </row>
@@ -1057,34 +1057,34 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MMBT3904 SOT-23</t>
+          <t>10k 0402</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Q1,Q2</t>
+          <t>R1,R2,R11,R25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C20526</t>
+          <t>C60490</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10k 0402</t>
+          <t>12k 0402 W5500 EXRES1 (12.4k spec OOS at LCSC; 12k within 100BASE-TX +-5%)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R1,R2,R6,R7,R11</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,19 +1094,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C60490</t>
+          <t>C25752</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>12k 0402 W5500 EXRES1 (12.4k spec OOS at LCSC; 12k within 100BASE-TX +-5%)</t>
+          <t>330R 0402</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4,R5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1116,19 +1116,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C25752</t>
+          <t>C2930002</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>330R 0402</t>
+          <t>5k1 0402</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R4,R5</t>
+          <t>R8,R9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1138,19 +1138,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C2930002</t>
+          <t>C25905</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5k1 0402</t>
+          <t>45.3k 0402 1% (buck FB top -&gt; 3.32V)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R8,R9</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1160,63 +1160,63 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C25905</t>
+          <t>C2933099</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>45.3k 0402 1% (buck FB top -&gt; 3.32V)</t>
+          <t>120R 0805 (DMX-A termination)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R12,R19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C2933099</t>
+          <t>C17437</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>120R 0805 (DMX-A termination)</t>
+          <t>1k 0402</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R12,R19</t>
+          <t>R13,R15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C17437</t>
+          <t>C106235</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1k 0402</t>
+          <t>150R 0402</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R13,R15</t>
+          <t>R14,R16,R17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1226,19 +1226,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C106235</t>
+          <t>C2909321</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>150R 0402</t>
+          <t>49.9R 1% 0402 W5500 TX center-tap bias</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R14,R16,R17</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1248,19 +1248,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C2909321</t>
+          <t>C25120</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>49.9R 1% 0402 W5500 TX center-tap bias</t>
+          <t>470R 0402 (DMX-A fail-safe bias)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R20,R21,R22,R23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C25120</t>
+          <t>C2909361</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>470R 0402 (DMX-A fail-safe bias)</t>
+          <t>30k 0402 1% (TPS2116 PR1 divider top, Vsw=4.0V)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R20,R21,R22,R23</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C2909361</t>
+          <t>C138008</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ESP32-S3-WROOM-1-N8 (8MB)</t>
+          <t>ESP32-S3-WROOM-1-N8R2 (8MB flash + 2MB quad PSRAM; quad keeps IO35/36/37 free, octal R8 would not)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C2913198</t>
+          <t>C2913204</t>
         </is>
       </c>
     </row>
@@ -1365,154 +1365,132 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CH340C USB-UART</t>
+          <t>SY8089 buck 5-&gt;3.3V</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SOP-16_L10.0-W3.9-P1.27-LS6.0-BL</t>
+          <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C7464026</t>
+          <t>C78988</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SY8089 buck 5-&gt;3.3V</t>
+          <t>ISO3086DWR isolated RS-485</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U5,U6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
+          <t>SOIC-16_L10.3-W7.5-P1.27-LS10.3-BL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C78988</t>
+          <t>C183095</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ISO3086DWR isolated RS-485</t>
+          <t>DP9900M-5V PoE PD + isolated DC-DC module (802.3af)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U5,U6</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SOIC-16_L10.3-W7.5-P1.27-LS10.3-BL</t>
+          <t>PWRM-SMD_DP9900M-5V</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>C183095</t>
+          <t>C5380106</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DP9900M-5V PoE PD + isolated DC-DC module (802.3af)</t>
+          <t>USBLC6-2SC6 USB ESD/TVS array (SOT-23-6)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PWRM-SMD_DP9900M-5V</t>
+          <t>SOT-23-6</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C5380106</t>
+          <t>C7519</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>USBLC6-2SC6 USB ESD/TVS array (SOT-23-6)</t>
+          <t>TPS2116DRLR ideal-diode power mux (USB/PoE 5V OR-ing)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>SOT-583-8</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>C7519</t>
+          <t>C3235557</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TPS2116DRLR ideal-diode power mux (USB/PoE 5V OR-ing)</t>
+          <t>25MHz crystal 3225 SMD (C9006 X322525MOB4SI, CL=12pF, mainstream/always-in-stock pkg)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SOT-583-8</t>
+          <t>Crystal_SMD_3225-4Pin_3.2x2.5mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>C3235557</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>25MHz crystal 2520 (CL=9pF; in-stock C2981624)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Crystal_SMD_2520-4Pin_2.5x2.0mm</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>C2981624</t>
+          <t>C9006</t>
         </is>
       </c>
     </row>
